--- a/docs/项目进度与开发计划.xlsx
+++ b/docs/项目进度与开发计划.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能点及完成进度" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="待开发功能" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="后续迭代方案" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="里程碑与迭代计划" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="接口与模块清单" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,7 +34,6 @@
       <sz val="14"/>
     </font>
     <font>
-      <i val="1"/>
       <color rgb="006B7280"/>
       <sz val="9"/>
     </font>
@@ -44,12 +43,20 @@
       <sz val="11"/>
     </font>
     <font>
+      <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="0015803D"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="004F46E5"/>
       <sz val="12"/>
     </font>
+    <font/>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -59,11 +66,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="004F46E5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DCFCE7"/>
       </patternFill>
     </fill>
   </fills>
@@ -93,23 +95,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -475,14 +478,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -495,7 +498,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>生成日期 2026-09-14 ｜ 后端 4 模块+1公共层 / 49 接口 / 小程序 28 页 / PC后台 25 页 ｜ 口径版本 v1.4（M8 已修复 4 个真实缺陷）</t>
+          <t>生成日期 2026-09-14 ｜ 后端 4 模块 / 56 接口（GET36·POST15·PUT5） ｜ 小程序 28 页 ｜ PC 后台 25 页 ｜ 口径 v1.6（M10 后）</t>
         </is>
       </c>
     </row>
@@ -534,7 +537,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>覆盖查询 / 覆盖需求登记（C端开放）</t>
+          <t>覆盖查询 / 覆盖需求登记 / 后台小区维护</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -549,7 +552,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>GET /api/community/check · POST /api/community/demand</t>
+          <t>GET /api/community/check · POST /api/community/demand · GET,POST /api/admin/communities</t>
         </is>
       </c>
     </row>
@@ -603,19 +606,19 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>sla/evaluate(-batch)/board/rules/compensations</t>
+          <t>/api/sla/evaluate(-batch)/board/rules/compensations</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>后端 · 套餐升级（product）</t>
+          <t>后端 · 工单与师傅（install）</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>一次性补差=月差×合约剩余月数 · 升级申请落库</t>
+          <t>工单池 · 工单详情 · 重置 · 师傅列表 · 容量配置</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -630,19 +633,19 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>package/detail · upgrade-options · upgrade</t>
+          <t>GET /api/admin/work-orders(/{id}) · POST reset · GET /api/admin/workers · POST worker-capacity</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>后端 · 流量监控（product）</t>
+          <t>后端 · 套餐与升级（product）</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>流量条 / 剩余 / 预警 / 7日趋势</t>
+          <t>在售列表 · 详情 · 升档选项 · 一次性补差=月差×合约剩余月数</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -657,19 +660,19 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>GET /api/traffic/usage</t>
+          <t>/api/package/list · detail · upgrade-options · POST upgrade</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>后端 · 在售套餐列表（M8新增）</t>
+          <t>后端 · 流量监控（product）</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>C端开放，返回主图</t>
+          <t>流量条 / 剩余 / 预警 / 7日趋势</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -684,19 +687,19 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>GET /api/package/list</t>
+          <t>GET /api/traffic/usage</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>后端 · 客户订单（M8新增）</t>
+          <t>后端 · 客户订单（product）</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>本人订单查询（C端开放）</t>
+          <t>本人订单查询（C端，已鉴权）</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -718,12 +721,12 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>后端 · RBAC 权限（system）</t>
+          <t>后端 · 后台聚合（product）</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>自研HS256 JWT · 实时查库授权 · 5角色/21权限码/26菜单 · 审计</t>
+          <t>客户 / 套餐 / 升级单 / 评价 / 销售 / 财务报表</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -738,19 +741,19 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>system 19接口(auth/users/roles/menus/logs/platform)</t>
+          <t>/api/admin/customers · packages · upgrade-orders · reviews · sales/report · finance/report</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>后端 · 小程序登录（M8修复）</t>
+          <t>后端 · RBAC 权限（system）</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>演示验证码1234 → 签发真实JWT</t>
+          <t>自研HS256 JWT · 实时查库授权 · 5角色/21权限码/26菜单 · 审计日志</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -765,19 +768,19 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>POST /api/auth/miniapp-login（permitAll）</t>
+          <t>系统模块 20 接口：auth / users / roles / menus / logs / platform</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>后端 · 数据库接入 MySQL</t>
+          <t>后端 · 微信登录双路径（M9新增）</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>25表 · 种子数据 · 启动自动建库 · 全部接口连库</t>
+          <t>配置 appid+secret 走 code2Session→openid 绑定客户；未配置回退演示码 1234</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -792,19 +795,19 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>schema.sql + data.sql（幂等）</t>
+          <t>WechatMiniAppService · POST /api/auth/miniapp-login（permitAll）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>后端 · 统一请求/错误处理（M8修复）</t>
+          <t>后端 · C端鉴权收口（M9）</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>非2xx一律reject（原静默吞错）</t>
+          <t>protect-client-api=true，C 端接口强制校验 JWT</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -819,19 +822,19 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>utils/api.js（客户端+师傅端）</t>
+          <t>JwtAuthFilter 新增 CUSTOMER 分支（CustomerPrincipal + ROLE_CUSTOMER）</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>客户端小程序 broadband-miniapp</t>
+          <t>后端 · 师傅端登录（M9新增）</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>20页：首页/服务/套餐(详情,列表,升级)/升级/小区查询/订单(地址,确认,列表,详情)/地址/流量/移机/自助/智慧家庭/评价/我的/设置/登录</t>
+          <t>按 worker.phone 查表签发 WORKER 令牌</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -846,19 +849,19 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>蓝#2563eb；已接真实契约（列表/订单/登录均修复）</t>
+          <t>POST /api/auth/worker-login（permitAll）</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>安装师傅端小程序 broadband-worker</t>
+          <t>后端 · WORKER 令牌鉴权（M9）</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>8页：工单/工单详情/完工确认/容量/排班/我的/登录</t>
+          <t>师傅令牌可访问工单/SLA 接口，与后台 RBAC 隔离</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -873,19 +876,19 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>橙#ea580c；getWorkOrder(404已修) + 真实登录</t>
+          <t>WorkerPrincipal + ROLE_WORKER + workorder:view + sla:view</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>PC后台 web-admin</t>
+          <t>后端 · 数据库接入 MySQL</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>25页/22路由：仪表盘/套餐/小区/工单/派单/容量/SLA/流量/升级/RBAC/客户/评价/审计/监控</t>
+          <t>25表 · 种子数据 · 启动自动初始化 · 全部接口连库</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -900,19 +903,19 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Vue3+ElementPlus按需+Pinia；按钮级v-perm；真实接口</t>
+          <t>schema.sql + data.sql（幂等）；M9 增列 customer.openid / worker.phone</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>文档套件</t>
+          <t>后端 · 统一请求/错误处理</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>5份说明书 v1.4/v1.3 + 模块文档(README/SLA/PKG_TRAFFIC/RBAC)</t>
+          <t>非2xx一律reject（原静默吞错）；401 自动跳登录页</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -927,166 +930,429 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>md+docx 已同步项目空间「文档」</t>
+          <t>utils/api.js（客户端 + 师傅端）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>客户端小程序 broadband-miniapp</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>20页：首页/服务/套餐(详情,列表,升级)/小区查询/订单(地址,确认,列表,详情)/地址/流量/移机/自助/智慧家庭/评价/我的/设置/登录</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>蓝#2563eb；登录走真实 miniapp-login，401 门禁已接</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>总体进度统计</t>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>安装师傅端小程序 broadband-worker</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>8页：首页/工单/工单详情/完工确认/容量/排班/我的/登录</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>橙#ea580c；登录改调真实 worker-login（原 mock 已废）</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>维度</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>已完成</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>规划中</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>覆盖率</t>
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>PC后台 web-admin</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>25页/22路由：仪表盘/套餐/小区/工单/派单/容量/SLA/流量/升级/RBAC/客户/评价/审计/监控</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Vue3+ElementPlus按需+Pinia；按钮级 v-perm；菜单由后端 /api/auth/me 动态渲染</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>后端业务模块</t>
+          <t>文档套件</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>4 + 1公共层</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>后端 REST 接口</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>49（GET31/POST13/PUT5）</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>100%</t>
+          <t>5份说明书 v1.4 + 模块文档(README/SLA/PKG_TRAFFIC/RBAC) + 本进度计划表 v1.5</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>md + docx 已同步项目空间「文档」</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>客户端小程序页</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>100%</t>
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>总体进度统计</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>安装师傅端小程序页</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>100%</t>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>维度</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>已完成</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>规划中</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>覆盖率</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>PC 后台页面</t>
+          <t>后端业务模块</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>25（22业务+login+403+404）</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
+          <t>4 + 1公共层</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
-        <is>
-          <t>100%</t>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>community / install / product / system + common</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
+          <t>后端 REST 接口</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>50（GET31 / POST14 / PUT5）</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>M9 新增 worker-login（49→50）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>数据库表</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>25 张 + 种子数据</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>M9 仅加列未加表</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>安全与鉴权</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>5角色 / 26菜单 / 21权限码</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>M9 扩至 3 类令牌：SYS / CUSTOMER / WORKER</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>客户端小程序页</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>20（含登录页）</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>设计稿 20 页全覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>安装师傅端小程序页</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>8（含登录页）</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>设计稿 8 页全覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>PC 后台页面</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>25（22业务 + login + 403 + 404）</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>设计稿 16 模块全覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
           <t>文档说明书</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>5 份 v1.4/v1.3</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>5 份 v1.4 + 进度计划表 v1.5</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>md/docx/xlsx 三格式</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>后端·师傅端接口层(M10)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>本人工单 + 详情 + 首页统计 + 容量看板 + 7天排班 + 完工提交</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>后端·师傅端数据隔离</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>服务端按 token 取 workerId 过滤，忽略客户端 workerId 传参</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>师傅端小程序</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>8 页全部接入真实接口（首页/工单/详情/完工/容量/排班/login）</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1107,247 +1373,331 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>宽带业务管理系统 · 待开发功能清单</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+          <t>宽带业务管理系统 · 待开发功能清单（截至 2026-09-14，M10 收口后）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>说明：#1 微信凭证待提供；#2 师傅端数据绑定已于 M10 完成（仅剩视觉截图验收）；优先级为建议值。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>待开发功能</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>当前状态</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>依赖 / 备注</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>小程序登录态正式收口</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>C端接口当前开放（protect-client-api=false），未真正鉴权</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>接微信 session 换 token；打开 protect-client-api 收口</t>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>建议优先级</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="n">
-        <v>2</v>
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>师傅端数据全绑定与视觉验收</t>
+          <t>微信真实凭证接入（AppID/Secret）</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>页面已建，部分数据链路/截图未验收</t>
+          <t>双路径已就绪，当前走演示码 1234 回退</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>无浏览器，需截图验收；绑定工单/容量/排班真实数据</t>
+          <t>用户提供小程序 AppID + Secret 后，自动切换 code2Session 真实登录</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="n">
-        <v>3</v>
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
+          <t>师傅端视觉验收（数据绑定已完成）</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>✅ 数据全绑定已完成（M10）</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>仅剩页面截图验收：无浏览器，需微信开发者工具导入 broadband-worker</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
           <t>业务闭环联调</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>下单→支付→派单→装机→SLA赔付→评价 未端到端打通</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>需微信支付/订单状态机串联</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>需订单状态机串联；与微信支付解耦可先跑通非支付链路</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>微信支付 / 真实支付闭环</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>未接入</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>需商户号 + 支付回调</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>需商户号 + 支付回调 + 幂等处理</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>监控深化（可观测性）</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>未做</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>metrics / 日志聚合 / 告警；设计稿「性能监控」页待接数据</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>配置治理</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>yml+环境变量，未做环境隔离</t>
-        </is>
-      </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>架构决策明确不引入 Apollo；做多环境 profile 治理</t>
+          <t>metrics / 日志聚合 / 告警；性能监控页接真实数据</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="n">
-        <v>7</v>
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
+          <t>配置治理（多环境 profile）</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>yml + 环境变量，未做环境隔离</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>架构决策：不引入 Apollo；做 dev/test/prod profile 隔离</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
           <t>CI/CD 流水线</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>未做</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>构建/测试/部署自动化</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>构建/测试/部署自动化；GitHub 仓库已建（linxi072/broadband）</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>压测与性能优化</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>未做</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>派单并发、DB 连接池、接口响应</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>派单并发、DB 连接池、接口响应时长</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>PC 后台扩展模块</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>销售管理、性能监控等设计稿已定义，部分未建页</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>对齐设计稿 v1.9 剩余模块</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>销售/财务/监控等页已建，部分数据深度不足</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>对齐设计稿 v1.9 剩余字段与图表</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>多端适配 / 国际化（可选）</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>未规划</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>视业务需要</t>
         </is>
       </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1359,135 +1709,483 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>宽带业务管理系统 · 后续更新迭代方案</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+          <t>宽带业务管理系统 · 里程碑与后续迭代计划</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>M1–M10 为已完成里程碑；M11 起为建议排期（相对周次，需负责人确认后定稿）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>里程碑</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>目标</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>关键交付物</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>时间 / 建议周期</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>风险 / 注意</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>M9 小程序鉴权收口</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>C端真正鉴权 + 师傅端全绑定 + 视觉验收</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>微信session换token；打开protect-client-api；师傅端截图验收；登录门禁打通</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>微信登录需小程序AppID/Secret；截图验收依赖浏览器环境</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>M10 业务闭环联调</t>
+          <t>M1 需求与设计稿</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>下单→支付→派单→装机→赔付→评价 端到端</t>
+          <t>需求梳理 + 高保真设计稿</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>微信支付接入；订单状态机；派单回写；SLA赔付；评价落库</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>支付回调与幂等；多状态一致性</t>
+          <t>broadband-design/index.html v1.9</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>M11 监控与配置治理</t>
+          <t>M2 后端核心算法 + 接口</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>可观测性 + 多环境配置</t>
+          <t>派单/SLA/补差算法与首批接口</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>metrics/日志/告警；多环境 profile；性能监控页接数据</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>监控组件选型；不引入Apollo的边界</t>
+          <t>3 模块 / 13 接口 / 6 个可运行 Demo</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>M12 CI/CD 与上线</t>
+          <t>M3 客户端小程序骨架</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
+          <t>客户端页面与请求封装</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>20 页（含登录页）+ api 封装</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>M4 数据库接入与联调</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>MySQL 持久化 + 真实联调</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>17 表 + 幂等初始化 + 端到端验证</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>M5 PC 后台落地</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Vue3 运营后台</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>web-admin 工程 + 22 业务页 + 22 路由</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>M6 安全体系</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>RBAC + JWT 鉴权</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>5 角色 / 21 权限码 / 鉴权矩阵实测 / 7 条单测</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>M7 小程序补页 + 登录态</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>客户端 20 页 + 师傅端 8 页</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>两个独立小程序工程 + 登录态骨架</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>M8 缺陷修复（小程序契约/登录）</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>修复 4 个真实缺陷</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>404/越权端点、静默吞错、mock 登录；接口 45→49</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>M9 双端登录态收口</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>C 端真正鉴权 + 师傅端真实登录</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>CUSTOMER/WORKER 令牌 · protect-client-api=true · miniapp-login 双路径 · worker-login；接口 49→50</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>微信真实凭证待提供（当前演示码回退）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>M10 师傅端数据绑定与验收</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>工单/排班/容量真实数据全绑定</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>WorkerController 6 接口 · 数据隔离 · 4 页真实绑定 · 接口 50→56</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>视觉验收待微信开发者工具截图</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>M11 业务闭环联调</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>下单→派单→装机→SLA→评价 端到端</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>订单状态机 · 派单回写 · SLA 赔付 · 评价落库</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>⬜ 规划中</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>建议 W2–W3</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>多状态一致性；支付可后置</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>M12 监控与配置治理</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>可观测性 + 多环境配置</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>metrics/日志/告警 · 多环境 profile · 监控页接数</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>⬜ 规划中</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>建议 W3–W4</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>监控组件选型；不引入 Apollo 的边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>M13 CI/CD 与上线</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
           <t>自动化构建部署 + 文档收尾</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>CI流水线；生产Nginx部署；5份文档最终版；复盘</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>生产密钥管理（jwt.secret 环境变量）</t>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>CI 流水线 · 生产 Nginx 部署 · 文档终版 · 复盘</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>⬜ 规划中</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>建议 W4–W5</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>生产密钥管理（jwt.secret 走环境变量）；GitHub 推送待 SSH 恢复</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1499,202 +2197,299 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="56" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>后端模块与接口清单（49 接口）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+          <t>后端模块与接口清单（56 接口 · GET36 / POST15 / PUT5）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>口径 v1.6（M10 后）：新增 WorkerController 6 个师傅端接口（本人工单/详情/summary/capacity/schedule/complete）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>模块</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>职责</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>接口数</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>方法分布</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>代表接口</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>community</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>小区覆盖查询/需求登记</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>GET1/POST1</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>/api/community/check · /api/community/demand</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>dispatch(install)</t>
+          <t>community</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>派单调度+容量</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>2</v>
+          <t>小区覆盖查询 / 需求登记 / 后台小区维护</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>POST1/GET1</t>
+          <t>GET2 / POST2</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>/api/dispatch/run · /api/dispatch/capacity</t>
+          <t>/api/community/check · /api/community/demand · /api/admin/communities(GET,POST)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>install/SLA</t>
+          <t>install · dispatch</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>装维时限/速率/赔付</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>5</v>
+          <t>派单调度 + 容量计算</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>POST2/GET3</t>
+          <t>POST1 / GET1</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>/api/sla/evaluate(-batch)/board/rules/compensations</t>
+          <t>/api/dispatch/run · /api/dispatch/capacity</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>install · SLA</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>套餐/升级/流量/客户订单/列表</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>8</v>
+          <t>装维时限 / 速率达标 / 赔付</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>GET5/POST3</t>
+          <t>POST2 / GET3</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>/api/package/* · /api/traffic/usage · /api/order/my</t>
+          <t>/api/sla/evaluate(-batch) · /board · /rules · /compensations</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>system(RBAC)</t>
+          <t>install · 工单与师傅</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>认证/用户/角色/菜单/日志/平台聚合/小程序登录</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>19</v>
+          <t>工单池 / 师傅 / 容量配置</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>GET12/POST5/PUT2</t>
+          <t>GET3 / POST2</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>/api/auth/* · /api/users/* · /api/roles/* · /api/menus · /api/logs · /api/platform · /api/auth/miniapp-login</t>
+          <t>/api/admin/work-orders(/{id}) · reset · /api/admin/workers · worker-capacity</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
+          <t>product</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>套餐 / 升级 / 流量 / 客户订单 / 后台聚合</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>GET11 / POST2 / PUT1</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>/api/package/* · /api/traffic/usage · /api/order/my · /api/admin/*</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>system（RBAC + 平台 + 登录）</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>认证 / 用户 / 角色 / 菜单 / 日志 / 平台聚合</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>GET11 / POST5 / PUT4</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>/api/auth/login · miniapp-login · worker-login · me · logout · /api/system/* · /api/admin/dashboard/*</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>公共层 common</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>主键生成 / 全局异常处理</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Ids · GlobalExceptionHandler</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>install · 师傅端 worker（M10 新增）</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>师傅本人数据：工单 / 统计 / 容量 / 排班 / 完工（服务端隔离）</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>GET5 / POST1</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>/api/worker/work-orders · /summary · /capacity · /schedule · /complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
           <t>合计</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>4模块+1公共层</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>49</v>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>GET31/POST13/PUT5</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>4 模块 + 1 公共层</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>GET36 / POST15 / PUT5</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>全部连库</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/项目进度与开发计划.xlsx
+++ b/docs/项目进度与开发计划.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,7 +54,6 @@
       <color rgb="004F46E5"/>
       <sz val="12"/>
     </font>
-    <font/>
   </fonts>
   <fills count="3">
     <fill>
@@ -95,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -112,7 +111,6 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -478,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -498,7 +496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>生成日期 2026-09-14 ｜ 后端 4 模块 / 56 接口（GET36·POST15·PUT5） ｜ 小程序 28 页 ｜ PC 后台 25 页 ｜ 口径 v1.6（M10 后）</t>
+          <t>生成日期 2026-09-14 ｜ 后端 4 模块+1公共层 / 56 接口 / 小程序 28 页 / PC后台 25 页 ｜ 口径版本 v1.6（M9 双端登录态收口 + M10 师傅端数据绑定与隔离 均已完成）</t>
         </is>
       </c>
     </row>
@@ -883,12 +881,12 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>后端 · 数据库接入 MySQL</t>
+          <t>后端 · 师傅端数据接口（M10新增）</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>25表 · 种子数据 · 启动自动初始化 · 全部接口连库</t>
+          <t>本人工单列表/详情 · 首页统计 · 容量看板 · 7天排班 · 完工提交</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -903,19 +901,19 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>schema.sql + data.sql（幂等）；M9 增列 customer.openid / worker.phone</t>
+          <t>WorkerController 6 接口 /api/worker/*；服务端按 token 隔离，忽略客户端 workerId 传参</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>后端 · 统一请求/错误处理</t>
+          <t>后端 · 数据库接入 MySQL</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>非2xx一律reject（原静默吞错）；401 自动跳登录页</t>
+          <t>25表 · 种子数据 · 启动自动初始化 · 全部接口连库</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -930,19 +928,19 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>utils/api.js（客户端 + 师傅端）</t>
+          <t>schema.sql + data.sql（幂等）；M9 增列 customer.openid / worker.phone</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>客户端小程序 broadband-miniapp</t>
+          <t>后端 · 统一请求/错误处理</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>20页：首页/服务/套餐(详情,列表,升级)/小区查询/订单(地址,确认,列表,详情)/地址/流量/移机/自助/智慧家庭/评价/我的/设置/登录</t>
+          <t>非2xx一律reject（原静默吞错）；401 自动跳登录页</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -957,19 +955,19 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>蓝#2563eb；登录走真实 miniapp-login，401 门禁已接</t>
+          <t>utils/api.js（客户端 + 师傅端）</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>安装师傅端小程序 broadband-worker</t>
+          <t>客户端小程序 broadband-miniapp</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>8页：首页/工单/工单详情/完工确认/容量/排班/我的/登录</t>
+          <t>20页：首页/服务/套餐(详情,列表,升级)/小区查询/订单(地址,确认,列表,详情)/地址/流量/移机/自助/智慧家庭/评价/我的/设置/登录</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -984,19 +982,19 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>橙#ea580c；登录改调真实 worker-login（原 mock 已废）</t>
+          <t>蓝#2563eb；登录走真实 miniapp-login，401 门禁已接</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>PC后台 web-admin</t>
+          <t>安装师傅端小程序 broadband-worker</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>25页/22路由：仪表盘/套餐/小区/工单/派单/容量/SLA/流量/升级/RBAC/客户/评价/审计/监控</t>
+          <t>8页：首页/工单/工单详情/完工确认/容量/排班/我的/登录</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -1011,107 +1009,107 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Vue3+ElementPlus按需+Pinia；按钮级 v-perm；菜单由后端 /api/auth/me 动态渲染</t>
+          <t>橙#ea580c；登录改调真实 worker-login（原 mock 已废）</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
+          <t>PC后台 web-admin</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>25页/22路由：仪表盘/套餐/小区/工单/派单/容量/SLA/流量/升级/RBAC/客户/评价/审计/监控</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Vue3+ElementPlus按需+Pinia；按钮级 v-perm；菜单由后端 /api/auth/me 动态渲染</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
           <t>文档套件</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>5份说明书 v1.4 + 模块文档(README/SLA/PKG_TRAFFIC/RBAC) + 本进度计划表 v1.5</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>✅ 已完成</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>md + docx 已同步项目空间「文档」</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>总体进度统计</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>维度</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>规划中</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>覆盖率</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>后端业务模块</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>4 + 1公共层</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>community / install / product / system + common</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>后端 REST 接口</t>
+          <t>后端业务模块</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>50（GET31 / POST14 / PUT5）</t>
+          <t>4 + 1公共层</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -1126,19 +1124,19 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>M9 新增 worker-login（49→50）</t>
+          <t>community / install / product / system + common</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>数据库表</t>
+          <t>后端 REST 接口</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>25 张 + 种子数据</t>
+          <t>56（GET36 / POST15 / PUT5）</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -1153,19 +1151,19 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>M9 仅加列未加表</t>
+          <t>M9 +worker-login（49→50）；M10 +6 个 /api/worker/*（50→56）</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>安全与鉴权</t>
+          <t>数据库表</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>5角色 / 26菜单 / 21权限码</t>
+          <t>25 张 + 种子数据</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -1180,19 +1178,19 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>M9 扩至 3 类令牌：SYS / CUSTOMER / WORKER</t>
+          <t>M9 仅加列未加表</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>客户端小程序页</t>
+          <t>安全与鉴权</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>20（含登录页）</t>
+          <t>5角色 / 26菜单 / 21权限码</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -1207,19 +1205,19 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>设计稿 20 页全覆盖</t>
+          <t>M9 扩至 3 类令牌：SYS / CUSTOMER / WORKER</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>安装师傅端小程序页</t>
+          <t>客户端小程序页</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>8（含登录页）</t>
+          <t>20（含登录页）</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -1234,19 +1232,19 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>设计稿 8 页全覆盖</t>
+          <t>设计稿 20 页全覆盖</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>PC 后台页面</t>
+          <t>安装师傅端小程序页</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>25（22业务 + login + 403 + 404）</t>
+          <t>8（含登录页）</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -1261,100 +1259,61 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>设计稿 16 模块全覆盖</t>
+          <t>设计稿 8 页全覆盖</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
+          <t>PC 后台页面</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>25（22业务 + login + 403 + 404）</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>设计稿 16 模块全覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
           <t>文档说明书</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>5 份 v1.4 + 进度计划表 v1.5</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>md/docx/xlsx 三格式</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>后端·师傅端接口层(M10)</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>本人工单 + 详情 + 首页统计 + 容量看板 + 7天排班 + 完工提交</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>✅ 已完成</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>后端·师傅端数据隔离</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>服务端按 token 取 workerId 过滤，忽略客户端 workerId 传参</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>✅ 已完成</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>师傅端小程序</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>8 页全部接入真实接口（首页/工单/详情/完工/容量/排班/login）</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>✅ 已完成</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>100%</t>
         </is>
       </c>
     </row>
@@ -1386,14 +1345,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>宽带业务管理系统 · 待开发功能清单（截至 2026-09-14，M10 收口后）</t>
+          <t>宽带业务管理系统 · 待开发功能清单（截至 2026-09-14，M9 收口后）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>说明：#1 微信凭证待提供；#2 师傅端数据绑定已于 M10 完成（仅剩视觉截图验收）；优先级为建议值。</t>
+          <t>说明：#1 已于 M9 完成并从待办移出；优先级为建议值，最终以负责人排期确认为准。</t>
         </is>
       </c>
     </row>
@@ -1459,17 +1418,17 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>师傅端视觉验收（数据绑定已完成）</t>
+          <t>师傅端页面视觉验收（M10b）</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>✅ 数据全绑定已完成（M10）</t>
+          <t>数据绑定已完成，页面截图验收未做</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>仅剩页面截图验收：无浏览器，需微信开发者工具导入 broadband-worker</t>
+          <t>需微信开发者工具导入 broadband-worker 后截图验收（无浏览器环境）</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -1709,7 +1668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1730,7 +1689,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>M1–M10 为已完成里程碑；M11 起为建议排期（相对周次，需负责人确认后定稿）</t>
+          <t>M1–M9 为已完成里程碑；M10 起为建议排期（相对周次，需负责人确认后定稿）。</t>
         </is>
       </c>
     </row>
@@ -2057,20 +2016,20 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>M10 师傅端数据绑定与验收</t>
+          <t>M10 师傅端数据绑定与隔离</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>工单/排班/容量真实数据全绑定</t>
+          <t>本人工单 + 统计/容量/排班/完工 真实数据</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>WorkerController 6 接口 · 数据隔离 · 4 页真实绑定 · 接口 50→56</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
+          <t>WorkerController 6 接口 · 服务端按 token 隔离（忽略客户端 workerId）· 4 个 mock 页面改真实数据 · 接口 50→56</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>✅ 已完成</t>
         </is>
@@ -2082,24 +2041,24 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>视觉验收待微信开发者工具截图</t>
+          <t>13 项验证全绿（含 5 项越权/隔离用例）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>M11 业务闭环联调</t>
+          <t>M10b 师傅端视觉验收</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>下单→派单→装机→SLA→评价 端到端</t>
+          <t>页面截图与交互验收</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>订单状态机 · 派单回写 · SLA 赔付 · 评价落库</t>
+          <t>微信开发者工具导入 broadband-worker 后逐页截图</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -2109,29 +2068,29 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>建议 W2–W3</t>
+          <t>建议 W1</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>多状态一致性；支付可后置</t>
+          <t>无浏览器环境，需人工验收</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>M12 监控与配置治理</t>
+          <t>M11 业务闭环联调</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>可观测性 + 多环境配置</t>
+          <t>下单→派单→装机→SLA→评价 端到端</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>metrics/日志/告警 · 多环境 profile · 监控页接数</t>
+          <t>订单状态机 · 派单回写 · SLA 赔付 · 评价落库</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -2141,42 +2100,74 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>建议 W3–W4</t>
+          <t>建议 W2–W3</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>监控组件选型；不引入 Apollo 的边界</t>
+          <t>多状态一致性；支付可后置</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
+          <t>M12 监控与配置治理</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>可观测性 + 多环境配置</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>metrics/日志/告警 · 多环境 profile · 监控页接数</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>⬜ 规划中</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>建议 W3–W4</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>监控组件选型；不引入 Apollo 的边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
           <t>M13 CI/CD 与上线</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>自动化构建部署 + 文档收尾</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>CI 流水线 · 生产 Nginx 部署 · 文档终版 · 复盘</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>⬜ 规划中</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>建议 W4–W5</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>生产密钥管理（jwt.secret 走环境变量）；GitHub 推送待 SSH 恢复</t>
         </is>
@@ -2217,7 +2208,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>口径 v1.6（M10 后）：新增 WorkerController 6 个师傅端接口（本人工单/详情/summary/capacity/schedule/complete）</t>
+          <t>口径 v1.6（M9 + M10 后）：新增 POST /api/auth/worker-login 与 6 个 /api/worker/* 接口，全部接口连库可用。</t>
         </is>
       </c>
     </row>
@@ -2359,106 +2350,108 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>product</t>
+          <t>install · 师傅端（M10新增）</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>套餐 / 升级 / 流量 / 客户订单 / 后台聚合</t>
+          <t>本人工单 / 首页统计 / 容量看板 / 排班 / 完工提交</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>GET11 / POST2 / PUT1</t>
+          <t>GET5 / POST1</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>/api/package/* · /api/traffic/usage · /api/order/my · /api/admin/*</t>
+          <t>/api/worker/work-orders(/{id}) · /summary · /capacity · /schedule · /{id}/complete</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>system（RBAC + 平台 + 登录）</t>
+          <t>product</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>认证 / 用户 / 角色 / 菜单 / 日志 / 平台聚合</t>
+          <t>套餐 / 升级 / 流量 / 客户订单 / 后台聚合</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>GET11 / POST5 / PUT4</t>
+          <t>GET11 / POST2 / PUT1</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>/api/auth/login · miniapp-login · worker-login · me · logout · /api/system/* · /api/admin/dashboard/*</t>
+          <t>/api/package/* · /api/traffic/usage · /api/order/my · /api/admin/*</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
+          <t>system（RBAC + 平台 + 登录）</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>认证 / 用户 / 角色 / 菜单 / 日志 / 平台聚合</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>GET11 / POST5 / PUT4</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>/api/auth/login · miniapp-login · worker-login · me · logout · /api/system/* · /api/admin/dashboard/*</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
           <t>公共层 common</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>主键生成 / 全局异常处理</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>Ids · GlobalExceptionHandler</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>install · 师傅端 worker（M10 新增）</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>师傅本人数据：工单 / 统计 / 容量 / 排班 / 完工（服务端隔离）</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>GET5 / POST1</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>/api/worker/work-orders · /summary · /capacity · /schedule · /complete</t>
         </is>
       </c>
     </row>
@@ -2473,8 +2466,10 @@
           <t>4 模块 + 1 公共层</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n">
-        <v>56</v>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>

--- a/docs/项目进度与开发计划.xlsx
+++ b/docs/项目进度与开发计划.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>生成日期 2026-09-14 ｜ 后端 4 模块+1公共层 / 56 接口 / 小程序 28 页 / PC后台 25 页 ｜ 口径版本 v1.6（M9 双端登录态收口 + M10 师傅端数据绑定与隔离 均已完成）</t>
+          <t>生成日期 2026-09-15 ｜ 后端 4 模块+1公共层 / 56 接口 / 小程序 28 页 / PC后台 25 页 ｜ 口径版本 v1.7（M9 双端登录态收口 + M10 师傅端数据绑定与隔离 已完成；微信 AppID 已就位，缺 AppSecret）</t>
         </is>
       </c>
     </row>
@@ -800,12 +800,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>后端 · C端鉴权收口（M9）</t>
+          <t>后端 · 微信 AppID 落地（M10）</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>protect-client-api=true，C 端接口强制校验 JWT</t>
+          <t>两端 project.config.json + 后端 application.yml 均写入真实 AppID</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -820,19 +820,19 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>JwtAuthFilter 新增 CUSTOMER 分支（CustomerPrincipal + ROLE_CUSTOMER）</t>
+          <t>AppID wxcc344ad7f4f849d4；AppSecret 仍由环境变量 WECHAT_SECRET 注入（未注入即走演示码回退）</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>后端 · 师傅端登录（M9新增）</t>
+          <t>后端 · C端鉴权收口（M9）</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>按 worker.phone 查表签发 WORKER 令牌</t>
+          <t>protect-client-api=true，C 端接口强制校验 JWT</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -847,19 +847,19 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>POST /api/auth/worker-login（permitAll）</t>
+          <t>JwtAuthFilter 新增 CUSTOMER 分支（CustomerPrincipal + ROLE_CUSTOMER）</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>后端 · WORKER 令牌鉴权（M9）</t>
+          <t>后端 · 师傅端登录（M9新增）</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>师傅令牌可访问工单/SLA 接口，与后台 RBAC 隔离</t>
+          <t>按 worker.phone 查表签发 WORKER 令牌</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -874,19 +874,19 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>WorkerPrincipal + ROLE_WORKER + workorder:view + sla:view</t>
+          <t>POST /api/auth/worker-login（permitAll）</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>后端 · 师傅端数据接口（M10新增）</t>
+          <t>后端 · WORKER 令牌鉴权（M9）</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>本人工单列表/详情 · 首页统计 · 容量看板 · 7天排班 · 完工提交</t>
+          <t>师傅令牌可访问工单/SLA 接口，与后台 RBAC 隔离</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -901,19 +901,19 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>WorkerController 6 接口 /api/worker/*；服务端按 token 隔离，忽略客户端 workerId 传参</t>
+          <t>WorkerPrincipal + ROLE_WORKER + workorder:view + sla:view</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>后端 · 数据库接入 MySQL</t>
+          <t>后端 · 师傅端数据接口（M10新增）</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>25表 · 种子数据 · 启动自动初始化 · 全部接口连库</t>
+          <t>本人工单列表/详情 · 首页统计 · 容量看板 · 7天排班 · 完工提交</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -928,19 +928,19 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>schema.sql + data.sql（幂等）；M9 增列 customer.openid / worker.phone</t>
+          <t>WorkerController 6 接口 /api/worker/*；服务端按 token 隔离，忽略客户端 workerId 传参</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>后端 · 统一请求/错误处理</t>
+          <t>后端 · 数据库接入 MySQL</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>非2xx一律reject（原静默吞错）；401 自动跳登录页</t>
+          <t>25表 · 种子数据 · 启动自动初始化 · 全部接口连库</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -955,19 +955,19 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>utils/api.js（客户端 + 师傅端）</t>
+          <t>schema.sql + data.sql（幂等）；M9 增列 customer.openid / worker.phone</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>客户端小程序 broadband-miniapp</t>
+          <t>后端 · 统一请求/错误处理</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>20页：首页/服务/套餐(详情,列表,升级)/小区查询/订单(地址,确认,列表,详情)/地址/流量/移机/自助/智慧家庭/评价/我的/设置/登录</t>
+          <t>非2xx一律reject（原静默吞错）；401 自动跳登录页</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -982,19 +982,19 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>蓝#2563eb；登录走真实 miniapp-login，401 门禁已接</t>
+          <t>utils/api.js（客户端 + 师傅端）</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>安装师傅端小程序 broadband-worker</t>
+          <t>客户端小程序 broadband-miniapp</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>8页：首页/工单/工单详情/完工确认/容量/排班/我的/登录</t>
+          <t>20页：首页/服务/套餐(详情,列表,升级)/小区查询/订单(地址,确认,列表,详情)/地址/流量/移机/自助/智慧家庭/评价/我的/设置/登录</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -1009,19 +1009,19 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>橙#ea580c；登录改调真实 worker-login（原 mock 已废）</t>
+          <t>蓝#2563eb；登录走真实 miniapp-login，401 门禁已接</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>PC后台 web-admin</t>
+          <t>安装师傅端小程序 broadband-worker</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>25页/22路由：仪表盘/套餐/小区/工单/派单/容量/SLA/流量/升级/RBAC/客户/评价/审计/监控</t>
+          <t>8页：首页/工单/工单详情/完工确认/容量/排班/我的/登录</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -1036,134 +1036,134 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Vue3+ElementPlus按需+Pinia；按钮级 v-perm；菜单由后端 /api/auth/me 动态渲染</t>
+          <t>橙#ea580c；登录改调真实 worker-login（原 mock 已废）</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
+          <t>PC后台 web-admin</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>25页/22路由：仪表盘/套餐/小区/工单/派单/容量/SLA/流量/升级/RBAC/客户/评价/审计/监控</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Vue3+ElementPlus按需+Pinia；按钮级 v-perm；菜单由后端 /api/auth/me 动态渲染</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>外部凭证与环境变量</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>AppID 已配置 / Secret 待注入；JWT 密钥、DB 凭据、C 端鉴权开关均已明确</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>🟡 90%</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>AppID wxcc344ad7f4f849d4（两端共用）；缺 WECHAT_SECRET 时自动回退演示码 1234</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
           <t>文档套件</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>5份说明书 v1.4 + 模块文档(README/SLA/PKG_TRAFFIC/RBAC) + 本进度计划表 v1.5</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>✅ 已完成</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>md + docx 已同步项目空间「文档」</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>5份说明书 + 模块文档 + 进度计划表 v1.7 + 设计稿 v2.1</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>md + docx + xlsx + html 已同步项目空间</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>总体进度统计</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>维度</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
         <is>
           <t>已完成</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>规划中</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="D29" s="3" t="inlineStr">
         <is>
           <t>覆盖率</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="E29" s="3" t="inlineStr">
         <is>
           <t>备注</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>后端业务模块</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>4 + 1公共层</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>community / install / product / system + common</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>后端 REST 接口</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>56（GET36 / POST15 / PUT5）</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>M9 +worker-login（49→50）；M10 +6 个 /api/worker/*（50→56）</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>数据库表</t>
+          <t>后端业务模块</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>25 张 + 种子数据</t>
+          <t>4 + 1公共层</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -1178,19 +1178,19 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>M9 仅加列未加表</t>
+          <t>community / install / product / system + common</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>安全与鉴权</t>
+          <t>后端 REST 接口</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>5角色 / 26菜单 / 21权限码</t>
+          <t>56（GET36 / POST15 / PUT5）</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -1205,19 +1205,19 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>M9 扩至 3 类令牌：SYS / CUSTOMER / WORKER</t>
+          <t>M9 +worker-login（49→50）；M10 +6 个 /api/worker/*（50→56）</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>客户端小程序页</t>
+          <t>数据库表</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>20（含登录页）</t>
+          <t>25 张 + 种子数据</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -1232,19 +1232,19 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>设计稿 20 页全覆盖</t>
+          <t>M9 仅加列未加表</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>安装师傅端小程序页</t>
+          <t>安全与鉴权</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>8（含登录页）</t>
+          <t>5角色 / 26菜单 / 21权限码</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -1259,19 +1259,19 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>设计稿 8 页全覆盖</t>
+          <t>M9 扩至 3 类令牌：SYS / CUSTOMER / WORKER</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>PC 后台页面</t>
+          <t>客户端小程序页</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>25（22业务 + login + 403 + 404）</t>
+          <t>20（含登录页）</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -1286,34 +1286,88 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>设计稿 16 模块全覆盖</t>
+          <t>设计稿 20 页全覆盖</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
+          <t>安装师傅端小程序页</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>8（含登录页）</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>设计稿 8 页全覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>PC 后台页面</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>25（22业务 + login + 403 + 404）</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>设计稿 16 模块全覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
           <t>文档说明书</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>5 份 v1.4 + 进度计划表 v1.5</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>说明书 v1.7（md/docx）+ 进度计划表 v1.7 + 设计稿 v2.1</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>md/docx/xlsx 三格式</t>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>md/docx/xlsx/html 四格式</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1345,14 +1399,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>宽带业务管理系统 · 待开发功能清单（截至 2026-09-14，M9 收口后）</t>
+          <t>宽带业务管理系统 · 待开发功能清单（截至 2026-09-15，M10 收尾后）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>说明：#1 已于 M9 完成并从待办移出；优先级为建议值，最终以负责人排期确认为准。</t>
+          <t>说明：原「微信真实凭证接入」已完成一半——AppID 已写入两端与后端配置，仅缺 AppSecret；优先级为建议值，最终以负责人排期确认为准。</t>
         </is>
       </c>
     </row>
@@ -1391,17 +1445,17 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>微信真实凭证接入（AppID/Secret）</t>
+          <t>微信 AppSecret 注入</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>双路径已就绪，当前走演示码 1234 回退</t>
+          <t>AppID 已配置（wxcc344ad7f4f849d4），登录仍走演示码 1234 回退</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>用户提供小程序 AppID + Secret 后，自动切换 code2Session 真实登录</t>
+          <t>提供 Secret 并导出环境变量 WECHAT_SECRET 后，自动切换 code2Session 真实登录，前端无需改动</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -1428,7 +1482,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>需微信开发者工具导入 broadband-worker 后截图验收（无浏览器环境）</t>
+          <t>需微信开发者工具导入 broadband-worker 后逐页截图验收（无浏览器环境）</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -1617,7 +1671,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>对齐设计稿 v1.9 剩余字段与图表</t>
+          <t>对齐设计稿 v2.1 剩余字段与图表</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -1634,20 +1688,47 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
+          <t>小程序 AppID 拆分（合规确认）</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>客户端与师傅端共用同一 AppID</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>提审前确认走「同主体多端」还是为师傅端单开 AppID</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
           <t>多端适配 / 国际化（可选）</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>未规划</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>视业务需要</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -1668,7 +1749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1689,7 +1770,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>M1–M9 为已完成里程碑；M10 起为建议排期（相对周次，需负责人确认后定稿）。</t>
+          <t>M1–M10 为已完成里程碑；M10b 起为建议排期（相对周次，需负责人确认后定稿）。代码已全量推送 GitHub（linxi072/broadband）。</t>
         </is>
       </c>
     </row>
@@ -2009,7 +2090,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>微信真实凭证待提供（当前演示码回退）</t>
+          <t>AppSecret 未注入，登录走演示码回退（AppID 已于 M10 补上）</t>
         </is>
       </c>
     </row>
@@ -2048,17 +2129,17 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>M10b 师傅端视觉验收</t>
+          <t>M10b 微信 AppSecret 接入</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>页面截图与交互验收</t>
+          <t>真实 code2Session 登录</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>微信开发者工具导入 broadband-worker 后逐页截图</t>
+          <t>导出 WECHAT_SECRET 环境变量，重启后端；验证 openid 落库与绑定客户</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -2068,29 +2149,29 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>建议 W1</t>
+          <t>随时（拿到 Secret 即刻）</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>无浏览器环境，需人工验收</t>
+          <t>Secret 属敏感项，不入库、不入文档</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>M11 业务闭环联调</t>
+          <t>M10c 师傅端视觉验收</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>下单→派单→装机→SLA→评价 端到端</t>
+          <t>页面截图与交互验收</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>订单状态机 · 派单回写 · SLA 赔付 · 评价落库</t>
+          <t>微信开发者工具导入 broadband-worker 后逐页截图</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -2100,29 +2181,29 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>建议 W2–W3</t>
+          <t>建议 W1</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>多状态一致性；支付可后置</t>
+          <t>无浏览器环境，需人工验收</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>M12 监控与配置治理</t>
+          <t>M11 业务闭环联调</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>可观测性 + 多环境配置</t>
+          <t>下单→派单→装机→SLA→评价 端到端</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>metrics/日志/告警 · 多环境 profile · 监控页接数</t>
+          <t>订单状态机 · 派单回写 · SLA 赔付 · 评价落库</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -2132,42 +2213,74 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>建议 W3–W4</t>
+          <t>建议 W2–W3</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>监控组件选型；不引入 Apollo 的边界</t>
+          <t>多状态一致性；支付可后置</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
+          <t>M12 监控与配置治理</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>可观测性 + 多环境配置</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>metrics/日志/告警 · 多环境 profile · 监控页接数</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>⬜ 规划中</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>建议 W3–W4</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>监控组件选型；不引入 Apollo 的边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
           <t>M13 CI/CD 与上线</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>自动化构建部署 + 文档收尾</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>CI 流水线 · 生产 Nginx 部署 · 文档终版 · 复盘</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>⬜ 规划中</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>建议 W4–W5</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>生产密钥管理（jwt.secret 走环境变量）；GitHub 推送待 SSH 恢复</t>
         </is>
@@ -2208,7 +2321,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>口径 v1.6（M9 + M10 后）：新增 POST /api/auth/worker-login 与 6 个 /api/worker/* 接口，全部接口连库可用。</t>
+          <t>口径 v1.7（M9 + M10 后）：新增 POST /api/auth/worker-login 与 6 个 /api/worker/* 接口；AppID wxcc344ad7f4f849d4 已回填，全部接口连库可用。</t>
         </is>
       </c>
     </row>

--- a/docs/项目进度与开发计划.xlsx
+++ b/docs/项目进度与开发计划.xlsx
@@ -496,7 +496,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>生成日期 2026-09-15 ｜ 后端 4 模块+1公共层 / 56 接口 / 小程序 28 页 / PC后台 25 页 ｜ 口径版本 v1.7（M9 双端登录态收口 + M10 师傅端数据绑定与隔离 已完成；微信 AppID 已就位，缺 AppSecret）</t>
+          <t>生成日期 2026-09-15 ｜ 后端 4 模块+1公共层 / 62 接口 / 小程序 28 页 / PC后台 25 页 ｜ 口径版本 v1.9（M9 双端登录态收口 + M10 师傅端数据绑定与隔离 已完成；M11 业务闭环联调已完成（接口 56→62）；M14 三端 UI 优化已完成（小程序双端）；微信 AppID 已就位，缺 AppSecret）</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>5份说明书 + 模块文档 + 进度计划表 v1.7 + 设计稿 v2.1</t>
+          <t>5份说明书 + 模块文档 + 进度计划表 v1.9 + 设计稿 v2.1</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>56（GET36 / POST15 / PUT5）</t>
+          <t>62（GET38 / POST19 / PUT5）</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -1205,7 +1205,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>M9 +worker-login（49→50）；M10 +6 个 /api/worker/*（50→56）</t>
+          <t>M9 +worker-login（49→50）；M10 +6 个 /api/worker/*（50→56）；M11 +6 个 订单/支付/追踪/评价/开工接口（56→62）；M14 三端 UI 优化（小程序双端）</t>
         </is>
       </c>
     </row>
@@ -1504,17 +1504,17 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>下单→支付→派单→装机→SLA赔付→评价 未端到端打通</t>
+          <t>✅ 已完成（已并入 M11 业务闭环联调：下单→支付→派单→装机→SLA赔付→评价 端到端打通，36 项断言全绿）</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>需订单状态机串联；与微信支付解耦可先跑通非支付链路</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>P0</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1749,7 +1749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1770,7 +1770,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>M1–M10 为已完成里程碑；M10b 起为建议排期（相对周次，需负责人确认后定稿）。代码已全量推送 GitHub（linxi072/broadband）。</t>
+          <t>M1–M11、M14 为已完成里程碑；M10b 起为建议排期（相对周次，需负责人确认后定稿）。代码已全量推送 GitHub（linxi072/broadband）。</t>
         </is>
       </c>
     </row>
@@ -2129,7 +2129,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>M10b 微信 AppSecret 接入</t>
+          <t>M10c 微信 AppSecret 接入</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -2161,7 +2161,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>M10c 师傅端视觉验收</t>
+          <t>M10b 师傅端视觉验收</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -2203,22 +2203,22 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>订单状态机 · 派单回写 · SLA 赔付 · 评价落库</t>
+          <t>订单状态机 · 派单回写 · 支付 seam · SLA 赔付 · 评价落库；接口 56→62（GET38/POST19/PUT5）；scripts/loop_test.py 端到端 36 项断言全绿</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>⬜ 规划中</t>
+          <t>✅ 已完成</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>建议 W2–W3</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>多状态一致性；支付可后置</t>
+          <t>支付目前为模拟（PayService seam），接真实微信支付 SDK 即切换</t>
         </is>
       </c>
     </row>
@@ -2283,6 +2283,38 @@
       <c r="F19" s="4" t="inlineStr">
         <is>
           <t>生产密钥管理（jwt.secret 走环境变量）；GitHub 推送待 SSH 恢复</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>M14 三端 UI 优化（小程序双端）</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>小程序双端设计系统 v2.0 + 缺失态补齐</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>客户端 11 骨架页重写 + 师傅端 8 页全量重写（橙主题）；web-admin 精致化延至第二批</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>无浏览器，需微信开发者工具截图验收</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2353,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>口径 v1.7（M9 + M10 后）：新增 POST /api/auth/worker-login 与 6 个 /api/worker/* 接口；AppID wxcc344ad7f4f849d4 已回填，全部接口连库可用。</t>
+          <t>口径 v1.9（M9 + M10 + M11 后）：新增 POST /api/auth/worker-login 与 6 个 /api/worker/* 接口；M11 新增 6 个订单/支付/追踪/评价/开工接口（共 62 个）；AppID wxcc344ad7f4f849d4 已回填，全部接口连库可用。</t>
         </is>
       </c>
     </row>
